--- a/annotation/Species_list_vs_CATAMI_2023_01.xlsx
+++ b/annotation/Species_list_vs_CATAMI_2023_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjansen\Desktop\science\SouthernOceanBiodiversityMapping\ARC_Data\annotation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CD8A5B-5DD6-4A12-A0D2-B75294CF0B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1559BFAB-B48F-464E-AEC0-F3DBFADD243F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15030" yWindow="-18120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="479">
   <si>
     <t>Label</t>
   </si>
@@ -1455,6 +1455,9 @@
   </si>
   <si>
     <t>Sponge_Erect_Other</t>
+  </si>
+  <si>
+    <t>Molluscs_Gastropods</t>
   </si>
 </sst>
 </file>
@@ -4232,6 +4235,9 @@
       <c r="J59" s="5" t="s">
         <v>473</v>
       </c>
+      <c r="K59" t="s">
+        <v>70</v>
+      </c>
       <c r="L59">
         <v>5</v>
       </c>
@@ -4240,6 +4246,9 @@
       </c>
       <c r="N59" s="5" t="s">
         <v>473</v>
+      </c>
+      <c r="O59" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
@@ -4507,6 +4516,9 @@
       <c r="N65" s="5" t="s">
         <v>473</v>
       </c>
+      <c r="O65" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -4551,6 +4563,9 @@
       <c r="N66" s="5" t="s">
         <v>473</v>
       </c>
+      <c r="O66" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
@@ -4595,6 +4610,9 @@
       <c r="N67" s="5" t="s">
         <v>473</v>
       </c>
+      <c r="O67" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -5176,6 +5194,9 @@
       <c r="M83">
         <v>2.5999999999999999E-2</v>
       </c>
+      <c r="O83" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
@@ -5213,6 +5234,9 @@
       </c>
       <c r="M84">
         <v>0.02</v>
+      </c>
+      <c r="O84" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">

--- a/annotation/Species_list_vs_CATAMI_2023_01.xlsx
+++ b/annotation/Species_list_vs_CATAMI_2023_01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjansen\Desktop\science\SouthernOceanBiodiversityMapping\ARC_Data\annotation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1559BFAB-B48F-464E-AEC0-F3DBFADD243F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359CEFEC-8977-4C0F-AE7C-A570F2EE4169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15030" yWindow="-18120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13770" yWindow="-18120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER_naming" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="487">
   <si>
     <t>Label</t>
   </si>
@@ -689,228 +689,63 @@
     <t>Macroalgae</t>
   </si>
   <si>
-    <t>Macroalgae Encrusting</t>
-  </si>
-  <si>
     <t>Encrusting</t>
   </si>
   <si>
-    <t>Anemone Colonial</t>
-  </si>
-  <si>
     <t>Colonial anemones</t>
   </si>
   <si>
-    <t>Anemone Solitary</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Anemone Colonial - Zoanthids</t>
-  </si>
-  <si>
     <t>Zoanthids</t>
   </si>
   <si>
-    <t>Ascidia Stalked Colonial - Other</t>
-  </si>
-  <si>
     <t>Ascidia</t>
   </si>
   <si>
     <t>Stalked Colonial</t>
   </si>
   <si>
-    <t>Ascidia Stalked Colonial - Morphotype 1 - Pinhead</t>
-  </si>
-  <si>
-    <t>Ascidia Stalked Colonial - Morphotype 2 - Long rod</t>
-  </si>
-  <si>
-    <t>Ascidia Stalked Solitary</t>
-  </si>
-  <si>
     <t>Stalked Solitary</t>
   </si>
   <si>
-    <t>Ascidia Unstalked Colonial</t>
-  </si>
-  <si>
     <t>Unstalked Colonial</t>
   </si>
   <si>
-    <t>Ascidia Unstalked Solitary</t>
-  </si>
-  <si>
     <t>Unstalked Solitary</t>
   </si>
   <si>
-    <t>Bryozoa Hard - Branching - Morphotype 1 - Antler</t>
-  </si>
-  <si>
     <t>Bryozoa</t>
   </si>
   <si>
     <t>Branching</t>
   </si>
   <si>
-    <t>Bryozoa Hard - Branching - Morphotype 2 - Coralhead</t>
-  </si>
-  <si>
-    <t>Bryozoa Hard - Branching - Morphotype 3 - Leafy</t>
-  </si>
-  <si>
-    <t>Bryozoa Hard - Branching - Morphotype 4 - Antler short</t>
-  </si>
-  <si>
-    <t>Bryozoa Hard - Encrusting</t>
-  </si>
-  <si>
-    <t>Bryozoa Hard - Fenestrate</t>
-  </si>
-  <si>
-    <t>Fenestrate</t>
-  </si>
-  <si>
-    <t>Bryozoa Hard - Massive</t>
-  </si>
-  <si>
-    <t>Massive</t>
-  </si>
-  <si>
-    <t>Bryozoa Hard - Melicerita obliqua</t>
-  </si>
-  <si>
     <t>Hard</t>
   </si>
   <si>
-    <t>Bryozoa Hard - Branching - Morphotype 4 - Purple</t>
-  </si>
-  <si>
-    <t>Bryozoa Soft - Dendroid</t>
-  </si>
-  <si>
-    <t>Dendroid</t>
-  </si>
-  <si>
-    <t>Bryozoa Soft - Morphotype 1 - Fan-shaped</t>
-  </si>
-  <si>
     <t>Soft</t>
   </si>
   <si>
-    <t>Bryozoa Soft - Foliaceous</t>
-  </si>
-  <si>
-    <t>Foliaceous</t>
-  </si>
-  <si>
     <t>Bryozoa - Unidentified Morphotype 1</t>
   </si>
   <si>
-    <t>Crustacea Amphipoda</t>
-  </si>
-  <si>
-    <t>Crustacea Barnacles</t>
-  </si>
-  <si>
     <t>Acorn</t>
   </si>
   <si>
-    <t>Crustacea Isopoda - Other</t>
-  </si>
-  <si>
-    <t>Crustacea Isopoda - Serolidae</t>
-  </si>
-  <si>
-    <t>Crustacea Prawns</t>
-  </si>
-  <si>
     <t>Prawn / shrimps / mysids</t>
   </si>
   <si>
-    <t>Echinoderms Asteridae - Other</t>
-  </si>
-  <si>
     <t>Echinoderms</t>
   </si>
   <si>
     <t>Sea stars</t>
   </si>
   <si>
-    <t>Echinoderms Asteridae - Morphotype 1 - Pentagon shape</t>
-  </si>
-  <si>
-    <t>Echinoderms Asteridae - Labidiaster annulatus</t>
-  </si>
-  <si>
-    <t>Echinoderms Crinoids - Stalked</t>
-  </si>
-  <si>
-    <t>Stalked crinoid</t>
-  </si>
-  <si>
-    <t>Echinoderms Crinoids - Unstalked</t>
-  </si>
-  <si>
-    <t>Unstalked crinoid</t>
-  </si>
-  <si>
-    <t>Echinoderms Echinoids - Irregular</t>
-  </si>
-  <si>
-    <t>Irregular urchins</t>
-  </si>
-  <si>
-    <t>Echinoderms Echinoids - Regular Other</t>
-  </si>
-  <si>
-    <t>Regular urchins</t>
-  </si>
-  <si>
-    <t>Echinoderms Echinoids - Regular Pencil urchins</t>
-  </si>
-  <si>
-    <t>Echinoderms Holothurians - Infaunal</t>
-  </si>
-  <si>
-    <t>Benthic</t>
-  </si>
-  <si>
-    <t>Echinoderms Holothurians - Other</t>
-  </si>
-  <si>
-    <t>Echinoderms Holothurians - Suspension Feeders Other</t>
-  </si>
-  <si>
-    <t>Echinoderms Holothurians - Suspension Feeders Buried Other</t>
-  </si>
-  <si>
-    <t>Echinoderms Holothurians - Suspension Feeders Buried - Morphotype 1 - Red</t>
-  </si>
-  <si>
-    <t>Echinoderms Ophiuroids - Morphotype 1 - Basketstarlike</t>
-  </si>
-  <si>
     <t>Brittle / snake stars</t>
   </si>
   <si>
-    <t>Echinoderms Ophiuroids - Basketstars</t>
-  </si>
-  <si>
     <t>Basket stars</t>
   </si>
   <si>
-    <t>Echinoderms Ophiuroids - Other</t>
-  </si>
-  <si>
-    <t>Echinoderms Ophiuroids - Suspension Feeders - Other</t>
-  </si>
-  <si>
-    <t>Echinoderms Ophiuroids - Suspension Feeders - Morphotype 1 - 6 Arms</t>
-  </si>
-  <si>
     <t>Fish - Rays &amp; Skates</t>
   </si>
   <si>
@@ -944,12 +779,6 @@
     <t>Hydrocorals</t>
   </si>
   <si>
-    <t>Hydrozoa - Hydroid Colonial</t>
-  </si>
-  <si>
-    <t>Hydrozoa - Hydroid Solitary</t>
-  </si>
-  <si>
     <t>Hydrozoa - Morphotype 2 - thin branching</t>
   </si>
   <si>
@@ -962,39 +791,21 @@
     <t>Jellies - Ctenophores</t>
   </si>
   <si>
-    <t>Molluscs Bivalves</t>
-  </si>
-  <si>
     <t>Molluscs</t>
   </si>
   <si>
     <t>Bivalves</t>
   </si>
   <si>
-    <t>Molluscs Cephalopods Octopods</t>
-  </si>
-  <si>
     <t>Octopods</t>
   </si>
   <si>
-    <t>Molluscs Chitons</t>
-  </si>
-  <si>
     <t>Chitons</t>
   </si>
   <si>
-    <t>Molluscs Gastropods No shells</t>
-  </si>
-  <si>
     <t>Gastropods</t>
   </si>
   <si>
-    <t>Molluscs Gastropods With shells - Other</t>
-  </si>
-  <si>
-    <t>Molluscs Gastropods With shells - Limpets</t>
-  </si>
-  <si>
     <t>Unidentifiable</t>
   </si>
   <si>
@@ -1019,72 +830,21 @@
     <t>Unidentified Morphotypes - Potentially suspension feeders</t>
   </si>
   <si>
-    <t>Octocorals 2D</t>
-  </si>
-  <si>
     <t>Black &amp; Octocorals</t>
   </si>
   <si>
     <t>Fan (2D)</t>
   </si>
   <si>
-    <t>Octocorals 2D - Fernfrond</t>
-  </si>
-  <si>
     <t>Fan (2D) Fern-frond</t>
   </si>
   <si>
-    <t>Octocorals Branching - Non-fleshy Bottlebrush Complex</t>
-  </si>
-  <si>
-    <t>Bottlebrush Complex</t>
-  </si>
-  <si>
-    <t>Octocorals Branching - Non-fleshy Bottlebrush Simple</t>
-  </si>
-  <si>
-    <t>Bottlebrush Simple</t>
-  </si>
-  <si>
-    <t>Octocorals 3D - Cuplike</t>
-  </si>
-  <si>
-    <t>Octocorals 3D - Fleshy Arborescent</t>
-  </si>
-  <si>
-    <t>Fleshy Arborescent</t>
-  </si>
-  <si>
-    <t>Octocorals Branching Fleshy Mushroom</t>
-  </si>
-  <si>
-    <t>Mushroom</t>
-  </si>
-  <si>
-    <t>Octocorals 3D - Non-Fleshy Arborescent</t>
-  </si>
-  <si>
-    <t>Non-Fleshy Arborescent</t>
-  </si>
-  <si>
-    <t>Octocorals 3D - Non-Fleshy Morphotype 1 - Strands</t>
-  </si>
-  <si>
-    <t>Non-Fleshy</t>
-  </si>
-  <si>
-    <t>Octocorals Seapen</t>
-  </si>
-  <si>
     <t>Quill (seapen)</t>
   </si>
   <si>
     <t>Octocorals - Morphotype 1 - Thin strand with large polyps</t>
   </si>
   <si>
-    <t>Octocorals Whip</t>
-  </si>
-  <si>
     <t>Whip</t>
   </si>
   <si>
@@ -1094,117 +854,15 @@
     <t>Siphonophores</t>
   </si>
   <si>
-    <t>Sponge Massive Forms Simple - Other</t>
-  </si>
-  <si>
     <t>Sponges</t>
   </si>
   <si>
-    <t>Massive Forms Simple</t>
-  </si>
-  <si>
-    <t>Sponge Massive Forms Simple - Morphotype 1 - Composite type</t>
-  </si>
-  <si>
-    <t>Sponge Massive Forms Simple - Large</t>
-  </si>
-  <si>
-    <t>Sponge Massive Forms Simple - Morphotype 2 - Orange</t>
-  </si>
-  <si>
-    <t>Sponge Massive Forms Ball - Other</t>
-  </si>
-  <si>
-    <t>Balls</t>
-  </si>
-  <si>
-    <t>Sponge Massive Forms Ball - Morphotype 1 - Long spicules</t>
-  </si>
-  <si>
-    <t>Sponge Cup-likes Barrel - Other</t>
-  </si>
-  <si>
-    <t>Barrels</t>
-  </si>
-  <si>
-    <t>Sponge Cup-likes Barrel - Small</t>
-  </si>
-  <si>
-    <t>Sponge Infaunal</t>
-  </si>
-  <si>
-    <t>Sponge Erect Forms - Branching - Morphotype 1 - Castlike</t>
-  </si>
-  <si>
-    <t>Erect Forms - Branching</t>
-  </si>
-  <si>
-    <t>Sponge Crusts Creeping</t>
-  </si>
-  <si>
     <t>Creeping / ramose</t>
   </si>
   <si>
-    <t>Sponge Cup-likes Cup</t>
-  </si>
-  <si>
-    <t>Cup / Goblet</t>
-  </si>
-  <si>
-    <t>Sponge Cup-likes Disc</t>
-  </si>
-  <si>
-    <t>Tables / discs</t>
-  </si>
-  <si>
-    <t>Sponge Crusts Encrusting</t>
-  </si>
-  <si>
-    <t>Sponge Erect Forms - Morphotype 1 - Bottlebrush</t>
-  </si>
-  <si>
     <t>Erect Forms</t>
   </si>
   <si>
-    <t>Sponge Erect Forms - Branching</t>
-  </si>
-  <si>
-    <t>Sponge Erect Forms - Laminar</t>
-  </si>
-  <si>
-    <t>Erect Forms - Laminar</t>
-  </si>
-  <si>
-    <t>Sponge Erect Forms - Palmate</t>
-  </si>
-  <si>
-    <t>Erect Forms - Palmate</t>
-  </si>
-  <si>
-    <t>Sponge Erect Forms - Simple</t>
-  </si>
-  <si>
-    <t>Erect Forms - Simple</t>
-  </si>
-  <si>
-    <t>Sponge Erect Forms - Stalked</t>
-  </si>
-  <si>
-    <t>Erect Forms - Stalked</t>
-  </si>
-  <si>
-    <t>Sponge Massive Forms Simple - Small</t>
-  </si>
-  <si>
-    <t>Sponge Massive Forms Simple - Morphotype 3 - Grey</t>
-  </si>
-  <si>
-    <t>Sponge Cup-likes Tubes</t>
-  </si>
-  <si>
-    <t>Tubes and chimneys</t>
-  </si>
-  <si>
     <t>Unidentified Morphotype 2</t>
   </si>
   <si>
@@ -1274,108 +932,27 @@
     <t>Worms - Other</t>
   </si>
   <si>
-    <t>Worms Polychaetes - Other</t>
-  </si>
-  <si>
     <t>Other Polychaetes</t>
   </si>
   <si>
-    <t>Worms Polychaetes - Scaleworms</t>
-  </si>
-  <si>
-    <t>Worms Polychaetes - Tubeworms</t>
-  </si>
-  <si>
     <t>Tube worms</t>
   </si>
   <si>
-    <t>Worms Pterobranchia</t>
-  </si>
-  <si>
-    <t>Worms Empty Tube</t>
-  </si>
-  <si>
-    <t>Worms Tube Deposit feeder</t>
-  </si>
-  <si>
     <t>Exclude_500m</t>
   </si>
   <si>
     <t>Exclude_2km</t>
   </si>
   <si>
-    <t>Crustacea Amphipoda - Other</t>
-  </si>
-  <si>
-    <t>Crustacea Amphipoda - Morphotype 1 - large</t>
-  </si>
-  <si>
-    <t>Crustacea Amphipoda - Morphotype 2 - grey</t>
-  </si>
-  <si>
-    <t>Crustacea Amphipoda - Morphotype 3 - elongated filaments</t>
-  </si>
-  <si>
-    <t>Crustacea King Crabs</t>
-  </si>
-  <si>
     <t>King Crabs</t>
   </si>
   <si>
-    <t>Echinoderms Ophiuroids - Morpthotype 2 - 6 Arms</t>
-  </si>
-  <si>
-    <t>Echinoderms Ophiuroids - Suspension Feeders - Morphotype 1 - 5 Arms</t>
-  </si>
-  <si>
-    <t>Echinoderms Ophiuroids - Suspension Feeders - Morphotype 2 - 5 Arms White</t>
-  </si>
-  <si>
-    <t>Echinoderms Ophiuroids - Suspension Feeders - Morphotype 3 - 6 Arms Red</t>
-  </si>
-  <si>
-    <t>Echinoderms Ophiuroids - Suspension Feeders - Morphotype 4 - 6 Arms White</t>
-  </si>
-  <si>
-    <t>Echinoderms Ophiuroids - Suspension Feeders - Morphotype 5 - 7 Arms</t>
-  </si>
-  <si>
-    <t>Echinoderms Ophiuroids - Morphotype 2 - Windy Arms</t>
-  </si>
-  <si>
-    <t>Echinoderms Holothurians - Suspension Feeders - Other</t>
-  </si>
-  <si>
-    <t>Echinoderms Holothurians - Suspension Feeders - Buried Other</t>
-  </si>
-  <si>
-    <t>Echinoderms Holothurians - Suspension Feeders - Buried Morphotype 1 - Red</t>
-  </si>
-  <si>
-    <t>Echinoderms Asteridae - Suspension Feeders</t>
-  </si>
-  <si>
-    <t>Echinoderms Asteridae - Morphotype 2 - Very small</t>
-  </si>
-  <si>
     <t>Rays &amp; Skates</t>
   </si>
   <si>
     <t>Jellies - Salps</t>
   </si>
   <si>
-    <t>Molluscs Gastropods With shells - Morphotype 1 - Limpets</t>
-  </si>
-  <si>
-    <t>Molluscs Gastropods With shells - Morphotype 2 - Limpets</t>
-  </si>
-  <si>
-    <t>Molluscs Gastropods With shells -  Spindle shell</t>
-  </si>
-  <si>
-    <t>Molluscs Gastropods With shells - Morphotype 3 - White brown</t>
-  </si>
-  <si>
     <t>Unidentified Morphotype 1 - Dark red</t>
   </si>
   <si>
@@ -1400,36 +977,18 @@
     <t>Seaspiders - Morphotype 1 - Thin legs</t>
   </si>
   <si>
-    <t>Worms Acorn</t>
-  </si>
-  <si>
     <t>Acorn worms</t>
   </si>
   <si>
-    <t>Worms Echiura</t>
-  </si>
-  <si>
     <t>Echiura</t>
   </si>
   <si>
-    <t>Worms Nemertea</t>
-  </si>
-  <si>
     <t>Worms - Morphotype 2 - In tube</t>
   </si>
   <si>
     <t>Worms - Morphotype 3 - Spikey skin</t>
   </si>
   <si>
-    <t>Worms Polychaetes - Scaleworms Other</t>
-  </si>
-  <si>
-    <t>Worms Polychaetes - Scaleworms Morphotype 1 - Purple</t>
-  </si>
-  <si>
-    <t>Worms Sipuncula</t>
-  </si>
-  <si>
     <t>Sipuncula</t>
   </si>
   <si>
@@ -1458,6 +1017,471 @@
   </si>
   <si>
     <t>Molluscs_Gastropods</t>
+  </si>
+  <si>
+    <t>Hydromedusae</t>
+  </si>
+  <si>
+    <t>Ctenophores</t>
+  </si>
+  <si>
+    <t>Branching Fleshy Arborescent</t>
+  </si>
+  <si>
+    <t>Branching Non-fleshy Bottlebrush Complex</t>
+  </si>
+  <si>
+    <t>Branching Non-fleshy Bottlebrush Simple</t>
+  </si>
+  <si>
+    <t>Branching Fleshy Mushroom</t>
+  </si>
+  <si>
+    <t>Branching Non-Fleshy Arborescent</t>
+  </si>
+  <si>
+    <t>Branching Non-Fleshy</t>
+  </si>
+  <si>
+    <t>Hard Branching</t>
+  </si>
+  <si>
+    <t>Hard Encrusting</t>
+  </si>
+  <si>
+    <t>Hard Fenestrate</t>
+  </si>
+  <si>
+    <t>Hard Massive</t>
+  </si>
+  <si>
+    <t>Soft Dendroid</t>
+  </si>
+  <si>
+    <t>Soft Foliaceous</t>
+  </si>
+  <si>
+    <t>Sea urchins Regular</t>
+  </si>
+  <si>
+    <t>Sea urchins Irregular</t>
+  </si>
+  <si>
+    <t>Sea cucumbers Benthic</t>
+  </si>
+  <si>
+    <t>Crinoid Unstalked</t>
+  </si>
+  <si>
+    <t>Crinoid Stalked</t>
+  </si>
+  <si>
+    <t>Massive forms Simple</t>
+  </si>
+  <si>
+    <t>Massive forms Balls</t>
+  </si>
+  <si>
+    <t>Cup-likes Barrels</t>
+  </si>
+  <si>
+    <t>Erect forms Branching</t>
+  </si>
+  <si>
+    <t>Cup-likes Cups Cup / Goblet</t>
+  </si>
+  <si>
+    <t>Cup-likes Cups Tables / discs</t>
+  </si>
+  <si>
+    <t>Crusts Encrusting</t>
+  </si>
+  <si>
+    <t>Erect forms Laminar</t>
+  </si>
+  <si>
+    <t>Erect forms Palmate</t>
+  </si>
+  <si>
+    <t>Erect forms Simple</t>
+  </si>
+  <si>
+    <t>Erect forms Stalked</t>
+  </si>
+  <si>
+    <t>Cup-likes Tubes and chimneys</t>
+  </si>
+  <si>
+    <t>Worms - Polychaetes - Other</t>
+  </si>
+  <si>
+    <t>Worms - Polychaetes - Scaleworms</t>
+  </si>
+  <si>
+    <t>Worms - Polychaetes - Tubeworms</t>
+  </si>
+  <si>
+    <t>Worms - Pterobranchia</t>
+  </si>
+  <si>
+    <t>Worms - Empty Tube</t>
+  </si>
+  <si>
+    <t>Worms - Tube Deposit feeder</t>
+  </si>
+  <si>
+    <t>Sponge - Cup-likes - Tubes</t>
+  </si>
+  <si>
+    <t>Sponge - Massive forms - Simple - Morphotype 3 - Grey</t>
+  </si>
+  <si>
+    <t>Sponge - Massive forms - Simple - Small</t>
+  </si>
+  <si>
+    <t>Sponge - Erect forms - Stalked</t>
+  </si>
+  <si>
+    <t>Sponge - Erect forms - Simple</t>
+  </si>
+  <si>
+    <t>Sponge - Erect forms - Palmate</t>
+  </si>
+  <si>
+    <t>Sponge - Erect forms - Laminar</t>
+  </si>
+  <si>
+    <t>Sponge - Erect forms - Branching</t>
+  </si>
+  <si>
+    <t>Sponge - Erect forms - Morphotype 1 - Bottlebrush</t>
+  </si>
+  <si>
+    <t>Sponge - Crusts - Encrusting</t>
+  </si>
+  <si>
+    <t>Sponge - Cup-likes - Cup</t>
+  </si>
+  <si>
+    <t>Sponge - Cup-likes - Disc</t>
+  </si>
+  <si>
+    <t>Sponge - Crusts - Creeping</t>
+  </si>
+  <si>
+    <t>Sponge - Erect forms - Branching - Morphotype 1 - Castlike</t>
+  </si>
+  <si>
+    <t>Sponge - Infaunal</t>
+  </si>
+  <si>
+    <t>Sponge - Cup-likes - Barrel - Small</t>
+  </si>
+  <si>
+    <t>Sponge - Cup-likes - Barrel - Other</t>
+  </si>
+  <si>
+    <t>Sponge - Massive forms - Ball - Morphotype 1 - Long spicules</t>
+  </si>
+  <si>
+    <t>Sponge - Massive forms - Ball - Other</t>
+  </si>
+  <si>
+    <t>Sponge - Massive forms - Simple - Morphotype 2 - Orange</t>
+  </si>
+  <si>
+    <t>Sponge - Massive forms - Simple - Large</t>
+  </si>
+  <si>
+    <t>Sponge - Massive forms - Simple - Morphotype 1 - Composite type</t>
+  </si>
+  <si>
+    <t>Sponge - Massive forms - Simple - Other</t>
+  </si>
+  <si>
+    <t>Octocorals - Whip</t>
+  </si>
+  <si>
+    <t>Octocorals - Seapen</t>
+  </si>
+  <si>
+    <t>Octocorals - 3D - Non-Fleshy - Arborescent</t>
+  </si>
+  <si>
+    <t>Octocorals - 3D - Non-Fleshy - Morphotype 1 - Strands</t>
+  </si>
+  <si>
+    <t>Octocorals - Branching - Fleshy - Mushroom</t>
+  </si>
+  <si>
+    <t>Octocorals - 3D - Fleshy - Arborescent</t>
+  </si>
+  <si>
+    <t>Octocorals - 3D - Cuplike</t>
+  </si>
+  <si>
+    <t>Octocorals - Branching - Non-fleshy - Bottlebrush - Simple</t>
+  </si>
+  <si>
+    <t>Octocorals - Branching - Non-fleshy - Bottlebrush - Complex</t>
+  </si>
+  <si>
+    <t>Octocorals - 2D - Fernfrond</t>
+  </si>
+  <si>
+    <t>Octocorals - 2D</t>
+  </si>
+  <si>
+    <t>Molluscs - Chitons</t>
+  </si>
+  <si>
+    <t>Molluscs - Cephalopods - Octopods</t>
+  </si>
+  <si>
+    <t>Molluscs - Bivalves</t>
+  </si>
+  <si>
+    <t>Hydrozoa - Hydroid - Solitary</t>
+  </si>
+  <si>
+    <t>Hydrozoa - Hydroid - Colonial</t>
+  </si>
+  <si>
+    <t>Echinoderms - Asteridae - Other</t>
+  </si>
+  <si>
+    <t>Echinoderms - Asteridae - Morphotype 1 - Pentagon shape</t>
+  </si>
+  <si>
+    <t>Echinoderms - Asteridae - Labidiaster annulatus</t>
+  </si>
+  <si>
+    <t>Echinoderms - Crinoids - Stalked</t>
+  </si>
+  <si>
+    <t>Echinoderms - Crinoids - Unstalked</t>
+  </si>
+  <si>
+    <t>Echinoderms - Echinoids - Irregular</t>
+  </si>
+  <si>
+    <t>Echinoderms - Echinoids - Regular Other</t>
+  </si>
+  <si>
+    <t>Echinoderms - Echinoids - Regular Pencil urchins</t>
+  </si>
+  <si>
+    <t>Echinoderms - Holothurians - Infaunal</t>
+  </si>
+  <si>
+    <t>Echinoderms - Holothurians - Other</t>
+  </si>
+  <si>
+    <t>Echinoderms - Holothurians - Suspension Feeders Other</t>
+  </si>
+  <si>
+    <t>Echinoderms - Holothurians - Suspension Feeders Buried Other</t>
+  </si>
+  <si>
+    <t>Echinoderms - Holothurians - Suspension Feeders Buried - Morphotype 1 - Red</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Morphotype 1 - Basketstarlike</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Basketstars</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Other</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Suspension Feeders - Other</t>
+  </si>
+  <si>
+    <t>Crustacea - Prawns</t>
+  </si>
+  <si>
+    <t>Crustacea - Isopoda - Serolidae</t>
+  </si>
+  <si>
+    <t>Crustacea - Isopoda - Other</t>
+  </si>
+  <si>
+    <t>Crustacea - Barnacles</t>
+  </si>
+  <si>
+    <t>Crustacea - Amphipoda</t>
+  </si>
+  <si>
+    <t>Bryozoa - Soft - Foliaceous</t>
+  </si>
+  <si>
+    <t>Bryozoa - Soft - Morphotype 1 - Fan-shaped</t>
+  </si>
+  <si>
+    <t>Bryozoa - Soft - Dendroid</t>
+  </si>
+  <si>
+    <t>Bryozoa - Hard - Melicerita obliqua</t>
+  </si>
+  <si>
+    <t>Bryozoa - Hard - Massive</t>
+  </si>
+  <si>
+    <t>Bryozoa - Hard - Fenestrate</t>
+  </si>
+  <si>
+    <t>Bryozoa - Hard - Encrusting</t>
+  </si>
+  <si>
+    <t>Bryozoa - Hard - Branching - Morphotype 4 - Antler short</t>
+  </si>
+  <si>
+    <t>Bryozoa - Hard - Branching - Morphotype 3 - Leafy</t>
+  </si>
+  <si>
+    <t>Bryozoa - Hard - Branching - Morphotype 2 - Coralhead</t>
+  </si>
+  <si>
+    <t>Bryozoa - Hard - Branching - Morphotype 1 - Antler</t>
+  </si>
+  <si>
+    <t>Ascidia - Unstalked - Solitary</t>
+  </si>
+  <si>
+    <t>Ascidia - Unstalked - Colonial</t>
+  </si>
+  <si>
+    <t>Ascidia - Stalked - Solitary</t>
+  </si>
+  <si>
+    <t>Ascidia - Stalked - Colonial - Morphotype 2 - Long rod</t>
+  </si>
+  <si>
+    <t>Ascidia - Stalked - Colonial - Morphotype 1 - Pinhead</t>
+  </si>
+  <si>
+    <t>Anemone - Colonial - Zoanthids</t>
+  </si>
+  <si>
+    <t>Anemone - Solitary</t>
+  </si>
+  <si>
+    <t>Anemone - Colonial</t>
+  </si>
+  <si>
+    <t>Macroalgae - Encrusting</t>
+  </si>
+  <si>
+    <t>Crustacea - Amphipoda - Other</t>
+  </si>
+  <si>
+    <t>Crustacea - Amphipoda - Morphotype 1 - large</t>
+  </si>
+  <si>
+    <t>Crustacea - Amphipoda - Morphotype 2 - grey</t>
+  </si>
+  <si>
+    <t>Crustacea - Amphipoda - Morphotype 3 - elongated filaments</t>
+  </si>
+  <si>
+    <t>Crustacea - King Crabs</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Morpthotype 2 - Six Arms</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Suspension Feeders - Morphotype 1 - Six Arms</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Morphotype 2 - Windy Arms</t>
+  </si>
+  <si>
+    <t>Echinoderms - Asteridae - Morphotype 2 - Very small</t>
+  </si>
+  <si>
+    <t>Echinoderms - Echinoids - Regular - Other</t>
+  </si>
+  <si>
+    <t>Echinoderms - Echinoids - Regular - Pencil urchins</t>
+  </si>
+  <si>
+    <t>Echinoderms - Asteridae - Suspension feeders</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Suspension feeders - Other</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Suspension feeders - Morphotype 1 - Five Arms</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Suspension feeders - Morphotype 2 - Five Arms White</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Suspension feeders - Morphotype 3 - six Arms Red</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Suspension feeders - Morphotype 4 - Six Arms White</t>
+  </si>
+  <si>
+    <t>Echinoderms - Ophiuroids - Suspension feeders - Morphotype 5 - Seven Arms</t>
+  </si>
+  <si>
+    <t>Echinoderms - Holothurians - Suspension feeders - Other</t>
+  </si>
+  <si>
+    <t>Echinoderms - Holothurians - Suspension feeders - Buried Other</t>
+  </si>
+  <si>
+    <t>Echinoderms - Holothurians - Suspension feeders - Buried Morphotype 1 - Red</t>
+  </si>
+  <si>
+    <t>Molluscs - Cephalopods-  Octopods</t>
+  </si>
+  <si>
+    <t>Molluscs - Gastropods - No shells</t>
+  </si>
+  <si>
+    <t>Molluscs - Gastropods - With shells - Other</t>
+  </si>
+  <si>
+    <t>Molluscs - Gastropods - With shells - Morphotype 1 - Limpets</t>
+  </si>
+  <si>
+    <t>Molluscs - Gastropods - With shells - Morphotype 2 - Limpets</t>
+  </si>
+  <si>
+    <t>Molluscs - Gastropods - With shells -  Spindle shell</t>
+  </si>
+  <si>
+    <t>Molluscs - Gastropods - With shells - Morphotype 3 - White brown</t>
+  </si>
+  <si>
+    <t>Molluscs - Gastropods - With shells - Limpets</t>
+  </si>
+  <si>
+    <t>Worms - Acorn</t>
+  </si>
+  <si>
+    <t>Worms - Echiura</t>
+  </si>
+  <si>
+    <t>Worms - Nemertea</t>
+  </si>
+  <si>
+    <t>Worms - Polychaetes - Scaleworms Other</t>
+  </si>
+  <si>
+    <t>Worms - Polychaetes - Scaleworms Morphotype 1 - Purple</t>
+  </si>
+  <si>
+    <t>Worms - Sipuncula</t>
+  </si>
+  <si>
+    <t>Ascidia - Stalked - Colonial - Other</t>
+  </si>
+  <si>
+    <t>Bryozoa - Hard - Branching - Morphotype 5 - Purple</t>
   </si>
 </sst>
 </file>
@@ -1974,7 +1998,7 @@
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="68.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
@@ -2016,7 +2040,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>425</v>
+        <v>305</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
@@ -2028,13 +2052,13 @@
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>426</v>
+        <v>306</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>471</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -2053,7 +2077,6 @@
       <c r="E2" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="F2" s="2"/>
       <c r="G2" s="3">
         <v>80300000</v>
       </c>
@@ -2081,13 +2104,13 @@
         <v>1E-3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>222</v>
+        <v>449</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>221</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G3" s="3">
         <v>80300926</v>
@@ -2116,12 +2139,11 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>224</v>
+        <v>448</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="F4" s="2"/>
+        <v>223</v>
+      </c>
       <c r="G4" s="3">
         <v>11500901</v>
       </c>
@@ -2149,12 +2171,9 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F5" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="E5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5">
         <v>121</v>
@@ -2180,13 +2199,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>228</v>
+        <v>446</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G6">
         <v>11284000</v>
@@ -2221,13 +2240,13 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>230</v>
+        <v>485</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G7" s="3">
         <v>35000906</v>
@@ -2256,13 +2275,13 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>233</v>
+        <v>445</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G8" s="3">
         <v>35000906</v>
@@ -2294,13 +2313,13 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>234</v>
+        <v>444</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G9" s="3">
         <v>35000906</v>
@@ -2329,13 +2348,13 @@
         <v>2.4E-2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>235</v>
+        <v>443</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="G10" s="3">
         <v>35000905</v>
@@ -2364,13 +2383,13 @@
         <v>0.13800000000000001</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>237</v>
+        <v>442</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="G11" s="3">
         <v>35000903</v>
@@ -2399,13 +2418,13 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>239</v>
+        <v>441</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="G12" s="3">
         <v>35000902</v>
@@ -2439,7 +2458,6 @@
       <c r="E13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="2"/>
       <c r="G13" s="3">
         <v>19100000</v>
       </c>
@@ -2450,7 +2468,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L13">
         <v>2</v>
@@ -2459,7 +2477,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
@@ -2473,13 +2491,13 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>241</v>
+        <v>440</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>243</v>
+        <v>340</v>
       </c>
       <c r="G14" s="3">
         <v>20000908</v>
@@ -2508,13 +2526,13 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>244</v>
+        <v>439</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>243</v>
+        <v>340</v>
       </c>
       <c r="G15" s="3">
         <v>20000908</v>
@@ -2543,13 +2561,13 @@
         <v>0.114</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>245</v>
+        <v>438</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>243</v>
+        <v>340</v>
       </c>
       <c r="G16" s="3">
         <v>20000908</v>
@@ -2578,13 +2596,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>246</v>
+        <v>437</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>243</v>
+        <v>340</v>
       </c>
       <c r="G17" s="3">
         <v>20000908</v>
@@ -2619,13 +2637,13 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>247</v>
+        <v>436</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>223</v>
+        <v>341</v>
       </c>
       <c r="G18" s="3">
         <v>20000902</v>
@@ -2654,13 +2672,13 @@
         <v>2.4E-2</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>248</v>
+        <v>435</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>249</v>
+        <v>342</v>
       </c>
       <c r="G19" s="3">
         <v>20000903</v>
@@ -2689,13 +2707,13 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>250</v>
+        <v>434</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>251</v>
+        <v>343</v>
       </c>
       <c r="G20" s="3">
         <v>20000904</v>
@@ -2724,13 +2742,13 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>252</v>
+        <v>433</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="G21" s="3">
         <v>20000901</v>
@@ -2759,13 +2777,13 @@
         <v>1.6E-2</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>254</v>
+        <v>486</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>243</v>
+        <v>340</v>
       </c>
       <c r="G22" s="3">
         <v>20000908</v>
@@ -2794,13 +2812,13 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>255</v>
+        <v>432</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>256</v>
+        <v>344</v>
       </c>
       <c r="G23" s="3">
         <v>20000906</v>
@@ -2829,13 +2847,13 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>257</v>
+        <v>431</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="G24" s="3">
         <v>20000905</v>
@@ -2864,13 +2882,13 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>259</v>
+        <v>430</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>260</v>
+        <v>345</v>
       </c>
       <c r="G25" s="3">
         <v>20000907</v>
@@ -2899,12 +2917,11 @@
         <v>0</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F26" s="2"/>
+        <v>230</v>
+      </c>
       <c r="G26" s="3">
         <v>20000000</v>
       </c>
@@ -2932,12 +2949,11 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>262</v>
+        <v>429</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F27" s="2"/>
       <c r="G27" s="3">
         <v>27000000</v>
       </c>
@@ -2948,7 +2964,7 @@
         <v>1.6E-2</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L27">
         <v>13</v>
@@ -2957,7 +2973,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -2971,13 +2987,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>263</v>
+        <v>428</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>151</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="G28" s="3">
         <v>27500902</v>
@@ -2989,7 +3005,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -2998,7 +3014,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -3012,12 +3028,11 @@
         <v>1E-3</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>265</v>
+        <v>427</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F29" s="2"/>
       <c r="G29" s="3">
         <v>27000000</v>
       </c>
@@ -3028,7 +3043,7 @@
         <v>2E-3</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L29">
         <v>2</v>
@@ -3037,7 +3052,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -3051,12 +3066,11 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>266</v>
+        <v>426</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F30" s="2"/>
       <c r="G30" s="3">
         <v>27000000</v>
       </c>
@@ -3067,7 +3081,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L30">
         <v>23</v>
@@ -3076,7 +3090,7 @@
         <v>0.05</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -3090,13 +3104,13 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>267</v>
+        <v>425</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>151</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="G31" s="3">
         <v>28000901</v>
@@ -3108,7 +3122,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L31">
         <v>73</v>
@@ -3117,7 +3131,7 @@
         <v>0.159</v>
       </c>
       <c r="N31" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
@@ -3131,13 +3145,13 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>269</v>
+        <v>408</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="G32" s="3">
         <v>25102000</v>
@@ -3149,7 +3163,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L32">
         <v>68</v>
@@ -3158,7 +3172,7 @@
         <v>0.14799999999999999</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -3172,13 +3186,13 @@
         <v>1E-3</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>272</v>
+        <v>409</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="G33" s="3">
         <v>25102000</v>
@@ -3190,7 +3204,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K33" t="s">
         <v>43</v>
@@ -3202,7 +3216,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O33" t="s">
         <v>43</v>
@@ -3219,13 +3233,13 @@
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>273</v>
+        <v>410</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="G34" s="3">
         <v>25102000</v>
@@ -3237,7 +3251,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L34">
         <v>23</v>
@@ -3246,7 +3260,7 @@
         <v>0.05</v>
       </c>
       <c r="N34" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
@@ -3260,13 +3274,13 @@
         <v>2E-3</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>274</v>
+        <v>411</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>275</v>
+        <v>350</v>
       </c>
       <c r="G35" s="3">
         <v>25001901</v>
@@ -3278,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>470</v>
+        <v>323</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3287,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>470</v>
+        <v>323</v>
       </c>
       <c r="P35" t="s">
-        <v>472</v>
+        <v>325</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
@@ -3304,13 +3318,13 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>276</v>
+        <v>412</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>277</v>
+        <v>349</v>
       </c>
       <c r="G36" s="3">
         <v>25001902</v>
@@ -3322,7 +3336,7 @@
         <v>0.22500000000000001</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L36">
         <v>138</v>
@@ -3331,7 +3345,7 @@
         <v>0.30099999999999999</v>
       </c>
       <c r="N36" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
@@ -3345,13 +3359,13 @@
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>278</v>
+        <v>413</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>279</v>
+        <v>347</v>
       </c>
       <c r="G37" s="3">
         <v>25200902</v>
@@ -3363,7 +3377,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L37">
         <v>45</v>
@@ -3372,7 +3386,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="N37" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
@@ -3386,13 +3400,13 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>280</v>
+        <v>414</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>281</v>
+        <v>346</v>
       </c>
       <c r="G38" s="3">
         <v>25200901</v>
@@ -3404,7 +3418,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L38">
         <v>24</v>
@@ -3413,7 +3427,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="N38" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
@@ -3427,13 +3441,13 @@
         <v>1.4E-2</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>282</v>
+        <v>415</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>281</v>
+        <v>346</v>
       </c>
       <c r="G39" s="3">
         <v>25200901</v>
@@ -3445,7 +3459,7 @@
         <v>4.7E-2</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L39">
         <v>38</v>
@@ -3454,7 +3468,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="N39" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
@@ -3468,13 +3482,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>283</v>
+        <v>416</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>284</v>
+        <v>348</v>
       </c>
       <c r="G40" s="3">
         <v>25400901</v>
@@ -3486,7 +3500,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K40" t="s">
         <v>52</v>
@@ -3498,7 +3512,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O40" t="s">
         <v>52</v>
@@ -3515,13 +3529,13 @@
         <v>3.1E-2</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>285</v>
+        <v>417</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>284</v>
+        <v>348</v>
       </c>
       <c r="G41" s="3">
         <v>25400901</v>
@@ -3533,7 +3547,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L41">
         <v>70</v>
@@ -3542,7 +3556,7 @@
         <v>0.153</v>
       </c>
       <c r="N41" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
@@ -3556,13 +3570,13 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>286</v>
+        <v>418</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>284</v>
+        <v>348</v>
       </c>
       <c r="G42" s="3">
         <v>25400901</v>
@@ -3574,7 +3588,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L42">
         <v>44</v>
@@ -3583,7 +3597,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="N42" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
@@ -3597,13 +3611,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>287</v>
+        <v>419</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>284</v>
+        <v>348</v>
       </c>
       <c r="G43" s="3">
         <v>25400901</v>
@@ -3615,7 +3629,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L43">
         <v>8</v>
@@ -3624,7 +3638,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="N43" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
@@ -3638,13 +3652,13 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>284</v>
+        <v>348</v>
       </c>
       <c r="G44" s="3">
         <v>25400901</v>
@@ -3656,7 +3670,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K44" t="s">
         <v>54</v>
@@ -3668,7 +3682,7 @@
         <v>3.9E-2</v>
       </c>
       <c r="N44" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O44" t="s">
         <v>54</v>
@@ -3685,13 +3699,13 @@
         <v>1.2E-2</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="G45" s="3">
         <v>25160901</v>
@@ -3703,7 +3717,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L45">
         <v>14</v>
@@ -3712,7 +3726,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="N45" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
@@ -3726,13 +3740,13 @@
         <v>1E-3</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>291</v>
+        <v>422</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>292</v>
+        <v>240</v>
       </c>
       <c r="G46" s="3">
         <v>25160902</v>
@@ -3744,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>470</v>
+        <v>323</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -3753,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>470</v>
+        <v>323</v>
       </c>
       <c r="P46" t="s">
-        <v>472</v>
+        <v>325</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
@@ -3770,13 +3784,13 @@
         <v>0.252</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>293</v>
+        <v>423</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="G47" s="3">
         <v>25160901</v>
@@ -3788,7 +3802,7 @@
         <v>0.47299999999999998</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L47">
         <v>258</v>
@@ -3797,7 +3811,7 @@
         <v>0.56200000000000006</v>
       </c>
       <c r="N47" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
@@ -3811,13 +3825,13 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>294</v>
+        <v>424</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="G48" s="3">
         <v>25160901</v>
@@ -3829,7 +3843,7 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L48">
         <v>85</v>
@@ -3838,7 +3852,7 @@
         <v>0.185</v>
       </c>
       <c r="N48" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
@@ -3852,13 +3866,13 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>295</v>
+        <v>456</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="G49" s="3">
         <v>25160901</v>
@@ -3870,7 +3884,7 @@
         <v>0.02</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L49">
         <v>14</v>
@@ -3879,7 +3893,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="N49" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
@@ -3893,13 +3907,13 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>296</v>
+        <v>241</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>298</v>
+        <v>242</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="G50" s="3">
         <v>37990030</v>
@@ -3911,7 +3925,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L50">
         <v>77</v>
@@ -3920,7 +3934,7 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="N50" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
@@ -3934,13 +3948,13 @@
         <v>1E-3</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>299</v>
+        <v>244</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>297</v>
+        <v>242</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>300</v>
+        <v>245</v>
       </c>
       <c r="G51" s="3">
         <v>37990083</v>
@@ -3969,12 +3983,9 @@
         <v>1E-3</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F52" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="E52" s="3"/>
       <c r="H52">
         <v>2</v>
       </c>
@@ -3982,7 +3993,7 @@
         <v>2E-3</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L52">
         <v>2</v>
@@ -3991,7 +4002,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="N52" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
@@ -4005,12 +4016,11 @@
         <v>9.4E-2</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F53" s="2"/>
+        <v>248</v>
+      </c>
       <c r="G53" s="3">
         <v>11001000</v>
       </c>
@@ -4038,12 +4048,9 @@
         <v>1E-3</v>
       </c>
       <c r="D54" t="s">
-        <v>304</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F54" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="E54" s="3"/>
       <c r="H54">
         <v>2</v>
       </c>
@@ -4051,7 +4058,7 @@
         <v>2E-3</v>
       </c>
       <c r="K54" t="s">
-        <v>474</v>
+        <v>327</v>
       </c>
       <c r="L54">
         <v>2</v>
@@ -4060,7 +4067,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="O54" t="s">
-        <v>474</v>
+        <v>327</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
@@ -4074,13 +4081,13 @@
         <v>7.9000000000000001E-2</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G55" s="3">
         <v>11077906</v>
@@ -4109,12 +4116,11 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>307</v>
+        <v>407</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F56" s="2"/>
+        <v>248</v>
+      </c>
       <c r="G56" s="3">
         <v>11001000</v>
       </c>
@@ -4142,12 +4148,11 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>308</v>
+        <v>406</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F57" s="2"/>
+        <v>248</v>
+      </c>
       <c r="G57" s="3">
         <v>11001000</v>
       </c>
@@ -4158,7 +4163,7 @@
         <v>1.6E-2</v>
       </c>
       <c r="K57" t="s">
-        <v>474</v>
+        <v>327</v>
       </c>
       <c r="L57">
         <v>10</v>
@@ -4167,7 +4172,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="O57" t="s">
-        <v>474</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
@@ -4181,12 +4186,9 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D58" t="s">
-        <v>309</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F58" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="E58" s="3"/>
       <c r="H58">
         <v>11</v>
       </c>
@@ -4194,7 +4196,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="K58" t="s">
-        <v>474</v>
+        <v>327</v>
       </c>
       <c r="L58">
         <v>8</v>
@@ -4203,7 +4205,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="O58" t="s">
-        <v>474</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
@@ -4217,12 +4219,11 @@
         <v>2E-3</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>310</v>
+        <v>253</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F59" s="2"/>
       <c r="G59" s="3">
         <v>80600903</v>
       </c>
@@ -4233,7 +4234,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K59" t="s">
         <v>70</v>
@@ -4245,7 +4246,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="N59" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O59" t="s">
         <v>70</v>
@@ -4262,12 +4263,14 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>311</v>
+        <v>254</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F60" s="2"/>
+      <c r="F60" s="2" t="s">
+        <v>332</v>
+      </c>
       <c r="G60" s="3">
         <v>11000901</v>
       </c>
@@ -4278,7 +4281,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K60" t="s">
         <v>70</v>
@@ -4290,7 +4293,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="N60" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O60" t="s">
         <v>70</v>
@@ -4307,12 +4310,14 @@
         <v>1E-3</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>312</v>
+        <v>255</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F61" s="2"/>
+      <c r="F61" s="2" t="s">
+        <v>333</v>
+      </c>
       <c r="G61" s="3">
         <v>12000000</v>
       </c>
@@ -4323,7 +4328,7 @@
         <v>2E-3</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K61" t="s">
         <v>70</v>
@@ -4335,7 +4340,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="N61" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O61" t="s">
         <v>70</v>
@@ -4352,13 +4357,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>313</v>
+        <v>405</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>315</v>
+        <v>257</v>
       </c>
       <c r="G62" s="3">
         <v>23199000</v>
@@ -4370,10 +4375,10 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K62" t="s">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="L62">
         <v>7</v>
@@ -4382,7 +4387,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N62" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
@@ -4396,13 +4401,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>316</v>
+        <v>404</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>317</v>
+        <v>258</v>
       </c>
       <c r="G63" s="3">
         <v>23650000</v>
@@ -4414,10 +4419,10 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K63" t="s">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="L63">
         <v>14</v>
@@ -4426,7 +4431,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="N63" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
@@ -4440,13 +4445,13 @@
         <v>1E-3</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>318</v>
+        <v>403</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>319</v>
+        <v>259</v>
       </c>
       <c r="G64" s="3">
         <v>23100000</v>
@@ -4458,10 +4463,10 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K64" t="s">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="L64">
         <v>4</v>
@@ -4470,7 +4475,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="N64" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
@@ -4484,13 +4489,13 @@
         <v>1E-3</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>320</v>
+        <v>472</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>321</v>
+        <v>260</v>
       </c>
       <c r="G65" s="3">
         <v>24000000</v>
@@ -4502,10 +4507,10 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K65" t="s">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="L65">
         <v>3</v>
@@ -4514,10 +4519,10 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="N65" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O65" t="s">
-        <v>478</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
@@ -4531,13 +4536,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>322</v>
+        <v>473</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>321</v>
+        <v>260</v>
       </c>
       <c r="G66" s="3">
         <v>24000000</v>
@@ -4549,10 +4554,10 @@
         <v>1.4E-2</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K66" t="s">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="L66">
         <v>13</v>
@@ -4561,10 +4566,10 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="N66" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O66" t="s">
-        <v>478</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
@@ -4578,13 +4583,13 @@
         <v>1E-3</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>323</v>
+        <v>478</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>321</v>
+        <v>260</v>
       </c>
       <c r="G67" s="3">
         <v>24000000</v>
@@ -4596,10 +4601,10 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K67" t="s">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="L67">
         <v>3</v>
@@ -4608,10 +4613,10 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="N67" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O67" t="s">
-        <v>478</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
@@ -4625,12 +4630,9 @@
         <v>0.24199999999999999</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F68" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="E68" s="3"/>
       <c r="H68">
         <v>490</v>
       </c>
@@ -4661,12 +4663,9 @@
         <v>0.05</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F69" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="E69" s="3"/>
       <c r="H69">
         <v>152</v>
       </c>
@@ -4697,12 +4696,9 @@
         <v>2.7E-2</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F70" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="E70" s="3"/>
       <c r="H70">
         <v>78</v>
       </c>
@@ -4733,12 +4729,9 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F71" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="E71" s="3"/>
       <c r="H71">
         <v>9</v>
       </c>
@@ -4769,12 +4762,9 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F72" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="E72" s="3"/>
       <c r="H72">
         <v>68</v>
       </c>
@@ -4799,12 +4789,9 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F73" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="E73" s="3"/>
       <c r="H73">
         <v>14</v>
       </c>
@@ -4835,12 +4822,9 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F74" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="E74" s="3"/>
       <c r="H74">
         <v>18</v>
       </c>
@@ -4871,12 +4855,9 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F75" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="E75" s="3"/>
       <c r="H75">
         <v>24</v>
       </c>
@@ -4907,13 +4888,13 @@
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>332</v>
+        <v>402</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>334</v>
+        <v>270</v>
       </c>
       <c r="G76" s="3">
         <v>11168912</v>
@@ -4942,13 +4923,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>401</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>336</v>
+        <v>271</v>
       </c>
       <c r="G77">
         <v>11168913</v>
@@ -4983,13 +4964,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>337</v>
+        <v>400</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G78" s="3">
         <v>11168907</v>
@@ -5001,7 +4982,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="K78" t="s">
-        <v>475</v>
+        <v>328</v>
       </c>
       <c r="L78">
         <v>13</v>
@@ -5021,13 +5002,13 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>339</v>
+        <v>399</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G79" s="3">
         <v>11168906</v>
@@ -5039,7 +5020,7 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="K79" t="s">
-        <v>475</v>
+        <v>328</v>
       </c>
       <c r="L79">
         <v>116</v>
@@ -5059,12 +5040,11 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F80" s="2"/>
+        <v>269</v>
+      </c>
       <c r="G80" s="3">
         <v>11168901</v>
       </c>
@@ -5098,13 +5078,13 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>397</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G81" s="3">
         <v>11168911</v>
@@ -5133,13 +5113,13 @@
         <v>1.9E-2</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>344</v>
+        <v>396</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="G82" s="3">
         <v>11168910</v>
@@ -5168,13 +5148,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>394</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="G83" s="3">
         <v>11168904</v>
@@ -5186,7 +5166,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="K83" t="s">
-        <v>476</v>
+        <v>329</v>
       </c>
       <c r="L83">
         <v>12</v>
@@ -5195,7 +5175,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="O83" t="s">
-        <v>476</v>
+        <v>329</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
@@ -5209,13 +5189,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D84" t="s">
-        <v>348</v>
+        <v>395</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G84" s="3">
         <v>11168903</v>
@@ -5227,7 +5207,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="K84" t="s">
-        <v>476</v>
+        <v>329</v>
       </c>
       <c r="L84">
         <v>9</v>
@@ -5236,7 +5216,7 @@
         <v>0.02</v>
       </c>
       <c r="O84" t="s">
-        <v>476</v>
+        <v>329</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
@@ -5250,13 +5230,13 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>350</v>
+        <v>393</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>351</v>
+        <v>272</v>
       </c>
       <c r="G85" s="3">
         <v>11168918</v>
@@ -5285,12 +5265,11 @@
         <v>1.2E-2</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>352</v>
+        <v>273</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F86" s="2"/>
+        <v>269</v>
+      </c>
       <c r="G86" s="3">
         <v>11168901</v>
       </c>
@@ -5318,13 +5297,13 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>354</v>
+        <v>274</v>
       </c>
       <c r="G87" s="3">
         <v>11168917</v>
@@ -5358,7 +5337,6 @@
       <c r="E88" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F88" s="2"/>
       <c r="G88" s="3">
         <v>33000000</v>
       </c>
@@ -5369,7 +5347,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L88">
         <v>53</v>
@@ -5378,7 +5356,7 @@
         <v>0.115</v>
       </c>
       <c r="N88" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
@@ -5392,13 +5370,13 @@
         <v>0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>355</v>
+        <v>275</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
       <c r="G89" s="3">
         <v>11090000</v>
@@ -5410,7 +5388,7 @@
         <v>1E-3</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L89">
         <v>1</v>
@@ -5419,7 +5397,7 @@
         <v>2E-3</v>
       </c>
       <c r="N89" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
@@ -5433,13 +5411,13 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="G90" s="3">
         <v>10000904</v>
@@ -5468,13 +5446,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="G91" s="3">
         <v>10000904</v>
@@ -5509,13 +5487,13 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="G92" s="3">
         <v>10000904</v>
@@ -5544,13 +5522,13 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="G93" s="3">
         <v>10000904</v>
@@ -5579,13 +5557,13 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="G94" s="3">
         <v>10000905</v>
@@ -5614,13 +5592,13 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="G95" s="3">
         <v>10000905</v>
@@ -5649,13 +5627,13 @@
         <v>2.4E-2</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="G96" s="3">
         <v>10000907</v>
@@ -5684,13 +5662,13 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="G97" s="3">
         <v>10000907</v>
@@ -5719,12 +5697,11 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F98" s="2"/>
+        <v>277</v>
+      </c>
       <c r="G98" s="3">
         <v>10000000</v>
       </c>
@@ -5758,13 +5735,13 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="G99" s="3">
         <v>10000915</v>
@@ -5793,13 +5770,13 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>373</v>
+        <v>278</v>
       </c>
       <c r="G100" s="3">
         <v>10000917</v>
@@ -5828,13 +5805,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="G101" s="3">
         <v>10000919</v>
@@ -5869,13 +5846,13 @@
         <v>0.01</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="G102" s="3">
         <v>10000920</v>
@@ -5907,10 +5884,10 @@
         <v>378</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>223</v>
+        <v>357</v>
       </c>
       <c r="G103" s="3">
         <v>10000902</v>
@@ -5939,13 +5916,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>380</v>
+        <v>279</v>
       </c>
       <c r="G104" s="3">
         <v>10000912</v>
@@ -5957,7 +5934,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="K104" t="s">
-        <v>477</v>
+        <v>330</v>
       </c>
       <c r="L104">
         <v>10</v>
@@ -5977,13 +5954,13 @@
         <v>2.7E-2</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="G105" s="3">
         <v>10000915</v>
@@ -6012,13 +5989,13 @@
         <v>2.4E-2</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="E106" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="F106" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="G106" s="3">
         <v>10000913</v>
@@ -6047,13 +6024,13 @@
         <v>2E-3</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="G107" s="3">
         <v>10000914</v>
@@ -6088,13 +6065,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>387</v>
+        <v>360</v>
       </c>
       <c r="G108" s="3">
         <v>10000916</v>
@@ -6106,7 +6083,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="K108" t="s">
-        <v>477</v>
+        <v>330</v>
       </c>
       <c r="L108">
         <v>11</v>
@@ -6126,13 +6103,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>389</v>
+        <v>361</v>
       </c>
       <c r="G109" s="3">
         <v>10000906</v>
@@ -6144,7 +6121,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="K109" t="s">
-        <v>477</v>
+        <v>330</v>
       </c>
       <c r="L109">
         <v>10</v>
@@ -6164,13 +6141,13 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="G110" s="3">
         <v>10000904</v>
@@ -6199,13 +6176,13 @@
         <v>1.4E-2</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="G111" s="3">
         <v>10000904</v>
@@ -6234,13 +6211,13 @@
         <v>1.4E-2</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
       <c r="G112" s="3">
         <v>10000911</v>
@@ -6269,12 +6246,9 @@
         <v>1.4E-2</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F113" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="E113" s="3"/>
       <c r="H113">
         <v>36</v>
       </c>
@@ -6299,12 +6273,9 @@
         <v>1.4E-2</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F114" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="E114" s="3"/>
       <c r="H114">
         <v>49</v>
       </c>
@@ -6329,13 +6300,13 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>396</v>
+        <v>282</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>398</v>
+        <v>283</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>284</v>
       </c>
       <c r="G115" s="3">
         <v>11290901</v>
@@ -6364,13 +6335,13 @@
         <v>0.30499999999999999</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>399</v>
+        <v>285</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>401</v>
+        <v>286</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="G116" s="3">
         <v>82001007</v>
@@ -6399,13 +6370,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>402</v>
+        <v>288</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>401</v>
+        <v>286</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="G117" s="3">
         <v>82001007</v>
@@ -6437,13 +6408,13 @@
         <v>0.121</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>403</v>
+        <v>289</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>403</v>
+        <v>286</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="G118" s="3">
         <v>82001003</v>
@@ -6472,13 +6443,13 @@
         <v>6.2E-2</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>404</v>
+        <v>290</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>405</v>
+        <v>291</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>406</v>
+        <v>292</v>
       </c>
       <c r="G119" s="3">
         <v>81002000</v>
@@ -6507,13 +6478,13 @@
         <v>0.23200000000000001</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>407</v>
+        <v>293</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>407</v>
+        <v>286</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="G120" s="3">
         <v>82001004</v>
@@ -6542,13 +6513,13 @@
         <v>0.75700000000000001</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>408</v>
+        <v>294</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>408</v>
+        <v>286</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>294</v>
       </c>
       <c r="G121" s="3">
         <v>82001013</v>
@@ -6577,13 +6548,13 @@
         <v>0.51300000000000001</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>409</v>
+        <v>295</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>409</v>
+        <v>286</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="G122" s="3">
         <v>82001006</v>
@@ -6612,13 +6583,13 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>410</v>
+        <v>296</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>410</v>
+        <v>286</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>296</v>
       </c>
       <c r="G123" s="3">
         <v>82001002</v>
@@ -6647,12 +6618,9 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F124" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="E124" s="3"/>
       <c r="H124">
         <v>317</v>
       </c>
@@ -6677,12 +6645,9 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F125" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="E125" s="3"/>
       <c r="H125">
         <v>74</v>
       </c>
@@ -6707,12 +6672,9 @@
         <v>0.14899999999999999</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F126" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="E126" s="3"/>
       <c r="H126">
         <v>263</v>
       </c>
@@ -6737,12 +6699,9 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F127" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="E127" s="3"/>
       <c r="H127">
         <v>150</v>
       </c>
@@ -6767,12 +6726,9 @@
         <v>0.36099999999999999</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F128" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="E128" s="3"/>
       <c r="H128">
         <v>464</v>
       </c>
@@ -6799,10 +6755,7 @@
       <c r="D129" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E129" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F129" s="2"/>
+      <c r="E129" s="3"/>
       <c r="H129">
         <v>731</v>
       </c>
@@ -6827,12 +6780,11 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>414</v>
+        <v>300</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F130" s="3"/>
       <c r="G130" s="3">
         <v>80600901</v>
       </c>
@@ -6843,7 +6795,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="J130" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K130" t="s">
         <v>143</v>
@@ -6855,7 +6807,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="N130" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O130" t="s">
         <v>143</v>
@@ -6872,12 +6824,11 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>415</v>
+        <v>301</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F131" s="3"/>
       <c r="G131" s="3">
         <v>80600901</v>
       </c>
@@ -6888,7 +6839,7 @@
         <v>0.22900000000000001</v>
       </c>
       <c r="J131" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L131">
         <v>153</v>
@@ -6897,7 +6848,7 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="N131" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.3">
@@ -6911,12 +6862,11 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>416</v>
+        <v>302</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F132" s="3"/>
       <c r="G132" s="3">
         <v>80600901</v>
       </c>
@@ -6927,7 +6877,7 @@
         <v>0.03</v>
       </c>
       <c r="J132" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L132">
         <v>27</v>
@@ -6936,7 +6886,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="N132" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.3">
@@ -6950,13 +6900,13 @@
         <v>2E-3</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>417</v>
+        <v>363</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F133" s="3" t="s">
-        <v>418</v>
+      <c r="F133" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="G133" s="3">
         <v>22000902</v>
@@ -6968,7 +6918,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J133" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K133" t="s">
         <v>143</v>
@@ -6980,7 +6930,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="N133" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O133" t="s">
         <v>143</v>
@@ -6997,13 +6947,13 @@
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>419</v>
+        <v>364</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F134" s="3" t="s">
-        <v>418</v>
+      <c r="F134" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="G134" s="3">
         <v>22000902</v>
@@ -7015,7 +6965,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J134" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L134">
         <v>39</v>
@@ -7024,7 +6974,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="N134" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.3">
@@ -7038,13 +6988,13 @@
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>420</v>
+        <v>365</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F135" s="3" t="s">
-        <v>421</v>
+      <c r="F135" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="G135" s="3">
         <v>22000901</v>
@@ -7056,7 +7006,7 @@
         <v>0.10100000000000001</v>
       </c>
       <c r="J135" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L135">
         <v>73</v>
@@ -7065,7 +7015,7 @@
         <v>0.159</v>
       </c>
       <c r="N135" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.3">
@@ -7079,12 +7029,11 @@
         <v>1E-3</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>422</v>
+        <v>366</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F136" s="3"/>
       <c r="G136" s="3">
         <v>80600901</v>
       </c>
@@ -7095,7 +7044,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J136" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K136" t="s">
         <v>143</v>
@@ -7107,7 +7056,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="N136" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O136" t="s">
         <v>143</v>
@@ -7124,13 +7073,13 @@
         <v>0.16600000000000001</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>423</v>
+        <v>367</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F137" s="3" t="s">
-        <v>421</v>
+      <c r="F137" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="G137" s="3">
         <v>22000901</v>
@@ -7142,7 +7091,7 @@
         <v>0.34200000000000003</v>
       </c>
       <c r="J137" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="L137">
         <v>200</v>
@@ -7151,7 +7100,7 @@
         <v>0.436</v>
       </c>
       <c r="N137" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.3">
@@ -7165,12 +7114,11 @@
         <v>2E-3</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>424</v>
+        <v>368</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F138" s="3"/>
       <c r="G138" s="3">
         <v>80600901</v>
       </c>
@@ -7181,7 +7129,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J138" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="K138" t="s">
         <v>143</v>
@@ -7193,7 +7141,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="N138" s="5" t="s">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="O138" t="s">
         <v>143</v>
@@ -7238,7 +7186,7 @@
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="69.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
@@ -7280,7 +7228,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>425</v>
+        <v>305</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
@@ -7292,13 +7240,13 @@
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>426</v>
+        <v>306</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>471</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -7317,7 +7265,6 @@
       <c r="E2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="3"/>
       <c r="G2" s="3">
         <v>19100000</v>
       </c>
@@ -7377,12 +7324,11 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F4" s="3"/>
       <c r="G4" s="3">
         <v>27000000</v>
       </c>
@@ -7410,7 +7356,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>151</v>
@@ -7442,13 +7388,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>263</v>
+        <v>428</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>264</v>
+      <c r="F6" s="2" t="s">
+        <v>235</v>
       </c>
       <c r="G6" s="3">
         <v>27500902</v>
@@ -7477,7 +7423,7 @@
         <v>4.7E-2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>151</v>
@@ -7509,7 +7455,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>151</v>
@@ -7541,12 +7487,11 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>265</v>
+        <v>427</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F9" s="3"/>
       <c r="G9" s="3">
         <v>27000000</v>
       </c>
@@ -7574,12 +7519,11 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>266</v>
+        <v>426</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F10" s="3"/>
       <c r="G10" s="3">
         <v>27000000</v>
       </c>
@@ -7607,13 +7551,13 @@
         <v>1E-3</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>432</v>
+      <c r="F11" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="G11" s="3">
         <v>28836000</v>
@@ -7642,13 +7586,13 @@
         <v>0.53300000000000003</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>267</v>
+        <v>425</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>268</v>
+      <c r="F12" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="G12" s="3">
         <v>28000901</v>
@@ -7677,13 +7621,13 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>289</v>
+        <v>421</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>290</v>
+        <v>237</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="G13" s="3">
         <v>25160901</v>
@@ -7712,13 +7656,13 @@
         <v>2E-3</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>291</v>
+        <v>422</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>292</v>
+        <v>237</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>240</v>
       </c>
       <c r="G14" s="3">
         <v>25160902</v>
@@ -7730,7 +7674,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>470</v>
+        <v>323</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -7739,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>470</v>
+        <v>323</v>
       </c>
       <c r="P14" t="s">
-        <v>472</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -7756,13 +7700,13 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>290</v>
+        <v>237</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="G15" s="3">
         <v>25160901</v>
@@ -7797,13 +7741,13 @@
         <v>0.90800000000000003</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>293</v>
+        <v>423</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>290</v>
+        <v>237</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="G16" s="3">
         <v>25160901</v>
@@ -7832,13 +7776,13 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>294</v>
+        <v>462</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>290</v>
+        <v>237</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="G17" s="3">
         <v>25160901</v>
@@ -7867,13 +7811,13 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>434</v>
+        <v>463</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>290</v>
+        <v>237</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="G18" s="3">
         <v>25160901</v>
@@ -7902,13 +7846,13 @@
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>290</v>
+        <v>237</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="G19" s="3">
         <v>25160901</v>
@@ -7937,13 +7881,13 @@
         <v>3.1E-2</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>436</v>
+        <v>465</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>290</v>
+        <v>237</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="G20" s="3">
         <v>25160901</v>
@@ -7972,13 +7916,13 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>290</v>
+        <v>237</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="G21" s="3">
         <v>25160901</v>
@@ -8007,13 +7951,13 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>290</v>
+        <v>237</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="G22" s="3">
         <v>25160901</v>
@@ -8042,13 +7986,13 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>290</v>
+        <v>237</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="G23" s="3">
         <v>25160901</v>
@@ -8077,13 +8021,13 @@
         <v>2.3E-2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>274</v>
+        <v>411</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>275</v>
+        <v>237</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>350</v>
       </c>
       <c r="G24" s="3">
         <v>25001901</v>
@@ -8112,13 +8056,13 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>276</v>
+        <v>412</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>277</v>
+        <v>237</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="G25" s="3">
         <v>25001902</v>
@@ -8147,13 +8091,13 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>283</v>
+        <v>416</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>284</v>
+        <v>237</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>348</v>
       </c>
       <c r="G26" s="3">
         <v>25400901</v>
@@ -8182,13 +8126,13 @@
         <v>0.17399999999999999</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>285</v>
+        <v>417</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>284</v>
+        <v>237</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>348</v>
       </c>
       <c r="G27" s="3">
         <v>25400901</v>
@@ -8217,13 +8161,13 @@
         <v>0.20699999999999999</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>284</v>
+        <v>237</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>348</v>
       </c>
       <c r="G28" s="3">
         <v>25400901</v>
@@ -8252,13 +8196,13 @@
         <v>3.9E-2</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>284</v>
+        <v>237</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>348</v>
       </c>
       <c r="G29" s="3">
         <v>25400901</v>
@@ -8287,13 +8231,13 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>284</v>
+        <v>237</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>348</v>
       </c>
       <c r="G30" s="3">
         <v>25400901</v>
@@ -8322,13 +8266,13 @@
         <v>0.378</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>269</v>
+        <v>408</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>271</v>
+        <v>237</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="G31" s="3">
         <v>25102000</v>
@@ -8357,13 +8301,13 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>272</v>
+        <v>409</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>271</v>
+        <v>237</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="G32" s="3">
         <v>25102000</v>
@@ -8392,13 +8336,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>271</v>
+        <v>237</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="G33" s="3">
         <v>25102000</v>
@@ -8433,13 +8377,13 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>273</v>
+        <v>410</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>271</v>
+        <v>237</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="G34" s="3">
         <v>25102000</v>
@@ -8468,13 +8412,13 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>271</v>
+        <v>237</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="G35" s="3">
         <v>25102000</v>
@@ -8503,13 +8447,13 @@
         <v>0.12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>278</v>
+        <v>413</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>279</v>
+        <v>237</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>347</v>
       </c>
       <c r="G36" s="3">
         <v>25200902</v>
@@ -8538,13 +8482,13 @@
         <v>0.13100000000000001</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>280</v>
+        <v>459</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>281</v>
+        <v>237</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>346</v>
       </c>
       <c r="G37" s="3">
         <v>25200901</v>
@@ -8573,13 +8517,13 @@
         <v>0.156</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>282</v>
+        <v>460</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>281</v>
+        <v>237</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>346</v>
       </c>
       <c r="G38" s="3">
         <v>25200901</v>
@@ -8608,13 +8552,13 @@
         <v>0.17699999999999999</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>300</v>
+        <v>245</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>300</v>
+        <v>242</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="G39" s="3">
         <v>37990083</v>
@@ -8643,13 +8587,13 @@
         <v>2E-3</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>445</v>
+        <v>308</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>298</v>
+        <v>242</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="G40" s="3">
         <v>37990030</v>
@@ -8678,12 +8622,11 @@
         <v>0.02</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>310</v>
+        <v>253</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F41" s="3"/>
       <c r="G41" s="3">
         <v>80600903</v>
       </c>
@@ -8711,12 +8654,11 @@
         <v>0.01</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>312</v>
+        <v>255</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F42" s="3"/>
       <c r="G42" s="3">
         <v>12000000</v>
       </c>
@@ -8744,12 +8686,11 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>311</v>
+        <v>254</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F43" s="3"/>
       <c r="G43" s="3">
         <v>11000901</v>
       </c>
@@ -8777,12 +8718,11 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>446</v>
+        <v>309</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F44" s="3"/>
       <c r="G44" s="3">
         <v>35100000</v>
       </c>
@@ -8793,7 +8733,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>470</v>
+        <v>323</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -8802,10 +8742,10 @@
         <v>0</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>470</v>
+        <v>323</v>
       </c>
       <c r="P44" t="s">
-        <v>472</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
@@ -8819,13 +8759,13 @@
         <v>0.01</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>313</v>
+        <v>405</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>315</v>
+        <v>256</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="G45" s="3">
         <v>23199000</v>
@@ -8854,13 +8794,13 @@
         <v>0.03</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>316</v>
+        <v>471</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>317</v>
+        <v>256</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>258</v>
       </c>
       <c r="G46" s="3">
         <v>23650000</v>
@@ -8889,13 +8829,13 @@
         <v>1.2E-2</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>318</v>
+        <v>403</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>319</v>
+        <v>256</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="G47" s="3">
         <v>23100000</v>
@@ -8924,13 +8864,13 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>320</v>
+        <v>472</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>321</v>
+        <v>256</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="G48" s="3">
         <v>24000000</v>
@@ -8959,13 +8899,13 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>322</v>
+        <v>473</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>321</v>
+        <v>256</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="G49" s="3">
         <v>24000000</v>
@@ -8994,13 +8934,13 @@
         <v>2E-3</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>321</v>
+        <v>256</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="G50" s="3">
         <v>24000000</v>
@@ -9035,13 +8975,13 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>321</v>
+        <v>256</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="G51" s="3">
         <v>24000000</v>
@@ -9076,13 +9016,13 @@
         <v>0.03</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>321</v>
+        <v>256</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="G52" s="3">
         <v>24000000</v>
@@ -9111,13 +9051,13 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>321</v>
+        <v>256</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="G53" s="3">
         <v>24000000</v>
@@ -9146,11 +9086,9 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>227</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="E54" s="3"/>
       <c r="H54">
         <v>516</v>
       </c>
@@ -9175,11 +9113,9 @@
         <v>2E-3</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>227</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="E55" s="3"/>
       <c r="H55">
         <v>4</v>
       </c>
@@ -9210,11 +9146,9 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>227</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="E56" s="3"/>
       <c r="H56">
         <v>119</v>
       </c>
@@ -9245,11 +9179,9 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>227</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="E57" s="3"/>
       <c r="H57">
         <v>11</v>
       </c>
@@ -9280,11 +9212,9 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>227</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="E58" s="3"/>
       <c r="H58">
         <v>14</v>
       </c>
@@ -9315,11 +9245,9 @@
         <v>0.129</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>227</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="E59" s="3"/>
       <c r="H59">
         <v>183</v>
       </c>
@@ -9344,11 +9272,9 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>227</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="E60" s="3"/>
       <c r="H60">
         <v>6</v>
       </c>
@@ -9379,12 +9305,11 @@
         <v>0.377</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>457</v>
+        <v>316</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F61" s="3"/>
       <c r="G61" s="3">
         <v>33000000</v>
       </c>
@@ -9412,12 +9337,11 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>458</v>
+        <v>317</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F62" s="3"/>
       <c r="G62" s="3">
         <v>33000000</v>
       </c>
@@ -9451,13 +9375,13 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>355</v>
+        <v>275</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>356</v>
+      <c r="F63" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="G63" s="3">
         <v>11090000</v>
@@ -9486,12 +9410,11 @@
         <v>0.62</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>414</v>
+        <v>300</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F64" s="3"/>
       <c r="G64" s="3">
         <v>80600901</v>
       </c>
@@ -9519,13 +9442,13 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>460</v>
+      <c r="F65" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="G65" s="3">
         <v>36110000</v>
@@ -9554,13 +9477,13 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>462</v>
+      <c r="F66" s="2" t="s">
+        <v>319</v>
       </c>
       <c r="G66" s="3">
         <v>17020000</v>
@@ -9589,12 +9512,11 @@
         <v>2.7E-2</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F67" s="3"/>
       <c r="G67" s="3">
         <v>80600901</v>
       </c>
@@ -9622,12 +9544,11 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>416</v>
+        <v>302</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F68" s="3"/>
       <c r="G68" s="3">
         <v>80600901</v>
       </c>
@@ -9655,12 +9576,11 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>464</v>
+        <v>320</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F69" s="3"/>
       <c r="G69" s="3">
         <v>80600901</v>
       </c>
@@ -9691,12 +9611,11 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>465</v>
+        <v>321</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F70" s="3"/>
       <c r="G70" s="3">
         <v>80600901</v>
       </c>
@@ -9724,12 +9643,11 @@
         <v>1.6E-2</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>424</v>
+        <v>368</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F71" s="3"/>
       <c r="G71" s="3">
         <v>80600901</v>
       </c>
@@ -9757,13 +9675,13 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>417</v>
+        <v>363</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>418</v>
+      <c r="F72" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="G72" s="3">
         <v>22000902</v>
@@ -9795,13 +9713,13 @@
         <v>0.09</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F73" s="3" t="s">
-        <v>418</v>
+      <c r="F73" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="G73" s="3">
         <v>22000902</v>
@@ -9830,13 +9748,13 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>418</v>
+      <c r="F74" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="G74" s="3">
         <v>22000902</v>
@@ -9865,13 +9783,13 @@
         <v>0.18099999999999999</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>420</v>
+        <v>365</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>421</v>
+      <c r="F75" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="G75" s="3">
         <v>22000901</v>
@@ -9900,13 +9818,13 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>469</v>
+      <c r="F76" s="2" t="s">
+        <v>322</v>
       </c>
       <c r="G76" s="3">
         <v>17000000</v>
